--- a/servers/maze_main_server_dev/conf.d/data/maze_toast_msg_info【迷宫-全局消息通知】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_toast_msg_info【迷宫-全局消息通知】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A71E1BE-CA65-411E-8DD4-FEA051665EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07A55B6-626F-45D9-BA52-BACD13B45EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D45DE7B0-9F51-49EC-9977-799CD7C7A1F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{D45DE7B0-9F51-49EC-9977-799CD7C7A1F9}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_toast_msg_info" sheetId="1" r:id="rId1"/>
@@ -152,9 +152,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>临时背包已过期，装备丢失</t>
-  </si>
-  <si>
     <t>临时背包装备不存在点击预览装备提示：</t>
   </si>
   <si>
@@ -166,6 +163,10 @@
   </si>
   <si>
     <t>选中的部分装备已经被分解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备不存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -311,9 +312,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -351,7 +352,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -457,7 +458,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -599,7 +600,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -781,7 +782,7 @@
         <v>28</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F8" s="7">
         <v>2</v>
@@ -838,10 +839,10 @@
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="7">
         <v>2</v>
@@ -860,10 +861,10 @@
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="7">
         <v>2</v>
